--- a/output/Data and Chart Outputs/sarawak_energy_annual.xlsx
+++ b/output/Data and Chart Outputs/sarawak_energy_annual.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -792,7 +793,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -828,7 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -924,7 +923,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -950,7 +949,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B3" t="n">
@@ -976,7 +975,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B4" t="n">
@@ -1002,7 +1001,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B5" t="n">
@@ -1028,7 +1027,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B6" t="n">
@@ -1054,7 +1053,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B7" t="n">
@@ -1080,7 +1079,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B8" t="n">
@@ -1106,7 +1105,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B9" t="n">
@@ -1132,7 +1131,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B10" t="n">
@@ -1158,7 +1157,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B11" t="n">
